--- a/docs/StaticEncounters.xlsx
+++ b/docs/StaticEncounters.xlsx
@@ -190,10 +190,10 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Solaceon Ruins Room 7</t>
+          <t>Solaceon Ruins Room 6, north-west dead end</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>(5, 4)</t>
+          <t>(2, 3)</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
@@ -1521,14 +1521,14 @@
           <t>Prison Bottle in the bag</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Clash</t>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>Directly below Jirachi (5, 3) in one small room. Move one</t>
+          <t>MOVED 2026-10-24 from Room 7 (5, 4), below Jirachi. The dead end holds nothing else</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2273,12 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Turnback Cave, Giratina's room</t>
+          <t>Victory Road B1F, the TM59 island (Surf)</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>(8, 13)</t>
+          <t>(14, 19)</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
@@ -2289,14 +2289,14 @@
           <t>Zacian and Zamazenta caught</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>Clash</t>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Giratina returns to this room after a Hall of Fame. Move Eternatus</t>
+          <t>MOVED 2026-10-24 from Turnback Cave's Giratina room (8, 13). Shares the island with the TM59 ball (13, 18); Moltres's portal is in a 1F room</t>
         </is>
       </c>
     </row>
@@ -3181,14 +3181,14 @@
           <t>Story; after a Hall of Fame if not caught</t>
         </is>
       </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>Clash</t>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>Shares its room with Eternatus (8, 13)</t>
+          <t>Eternatus moved out on 2026-10-24</t>
         </is>
       </c>
     </row>
@@ -3973,14 +3973,14 @@
           <t>Three wishes granted</t>
         </is>
       </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>Clash</t>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>Directly above Hoopa (5, 4)</t>
+          <t>Hoopa moved to Room 6 on 2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4932,44 +4932,44 @@
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Solaceon Ruins Room 7</t>
+          <t>Solaceon Ruins</t>
         </is>
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Hoopa (5, 4); Jirachi (5, 3)</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>Clash</t>
+          <t>Jirachi (Room 7, 5, 3); Hoopa (Room 6 north-west dead end, 2, 3)</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>Move one, e.g. Hoopa to another Unown room</t>
+          <t>Settled 2026-10-24: Hoopa moved to Room 6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>Turnback Cave, Giratina's room</t>
+          <t>Turnback Cave / Victory Road B1F</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Eternatus (8, 13); Giratina (after a Hall of Fame)</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>Clash</t>
+          <t>Giratina (its room); Eternatus (Victory Road B1F, 14, 19)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>Move Eternatus</t>
+          <t>Settled 2026-10-24: Eternatus moved to Victory Road B1F</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
           <t>Kyurem (Iceberg doorway room, 7, 5); Regice's ruins; Cosmog (35, 21); Articuno portal (to place); Kyogre (B1F); Totem Kommo-o (6F)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5050,7 +5050,7 @@
           <t>Virizion (80, 10); Xerneas (70, 14); Totem Vikavolt (22, 68); Celebi portals (to place)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5072,7 +5072,7 @@
           <t>Totem Marowak (3, 4); Ho-Oh portal (to place)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5094,7 +5094,7 @@
           <t>Totem Mimikyu (26, 10); Marshadow (21, 9)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5116,7 +5116,7 @@
           <t>Totem Togedemaru (10, 7); Victini (2, 7); Electric Master (4, 3)</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5138,7 +5138,7 @@
           <t>Totem Salazzle (181, 585); Chi-Yu (180, 593) and stakes 7–8</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5160,7 +5160,7 @@
           <t>Totem Ribombee (18, 43); Tapu Bulu (24, 36)</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5182,7 +5182,7 @@
           <t>Totem Araquanid (713, 826); Suicune (689, 826)</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5204,7 +5204,7 @@
           <t>Tapu Fini (716, 345); Wyver (717, 346)</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5226,7 +5226,7 @@
           <t>Diancie (2, 22); Meltan (5, 20); Melmetal (5, 24)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5248,7 +5248,7 @@
           <t>Tapu Lele (13, 12); Cresselia then Latias/Latios (16, 15)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5270,7 +5270,7 @@
           <t>Koraidon (29, 36); Miraidon (27, 37); Terapagos (30, 34)</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5292,7 +5292,7 @@
           <t>Zygarde (B1F 21, 4); Necrozma (1F 70, 9); Mira's quest</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5314,7 +5314,7 @@
           <t>Magearna (11, 13); Volkner</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5336,7 +5336,7 @@
           <t>Kubfu (13, 17); the Gym puzzle</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5358,7 +5358,7 @@
           <t>Calyrex (461, 527); the elder, the ruins path</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5380,7 +5380,7 @@
           <t>Meloetta (27, 8)</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -5402,7 +5402,7 @@
           <t>Enamorus (912, 535); Pecharunt (898, 526); Shaymin tablet (908, 491)</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -5424,7 +5424,7 @@
           <t>Yveltal (813, 426); Gene (827, 438)</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/docs/StaticEncounters.xlsx
+++ b/docs/StaticEncounters.xlsx
@@ -1217,12 +1217,12 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Route 228, Rock Peak Ruins chamber</t>
+          <t>Route 228, north end of the first sand field</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>(7, 5)</t>
+          <t>(782, 323)</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
@@ -1233,14 +1233,14 @@
           <t>Tornadus and Thundurus in the party</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Clash</t>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Two tiles from Regidrago (5, 6), in Regirock's puzzle chamber. Check the statue and dots</t>
+          <t>MOVED 2026-10-24 from the Rock Peak Ruins doorway room (7, 5). Ace Trainer Jose (779, 325) looks west/east on another row</t>
         </is>
       </c>
     </row>
@@ -2573,14 +2573,14 @@
           <t>Regirock, Regice, Registeel in the party</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Clash</t>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Two tiles from Landorus (7, 5), in Regirock's puzzle chamber</t>
+          <t>Landorus moved outside on 2026-10-24</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>Rock Peak: Landorus and Regidrago in the chamber. Iceberg: Kyurem's doorway room</t>
+          <t>Iceberg: Kyurem's doorway room. Rock Peak is settled (Landorus moved)</t>
         </is>
       </c>
     </row>
@@ -4976,22 +4976,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Route 228, Rock Peak Ruins chamber</t>
+          <t>Route 228</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Landorus (7, 5); Regidrago (5, 6); Regirock's statue and dots</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Clash</t>
+          <t>Landorus (782, 323, outside); Regidrago (Rock Peak Ruins doorway room, 5, 6)</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Check the tiles against the puzzle, or move one</t>
+          <t>Settled 2026-10-24: Landorus moved to the sand field</t>
         </is>
       </c>
     </row>

--- a/docs/StaticEncounters.xlsx
+++ b/docs/StaticEncounters.xlsx
@@ -591,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -620,6 +620,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4078,12 +4079,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Articuno</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>Renegade (not ported yet)</t>
+          <t>Manaphy</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>Renegade (ported)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -4093,30 +4094,30 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Mt. Coronet summit portal</t>
+          <t>Pokémon Mansion, Mr. Backlot's office</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>to place</t>
+          <t>(18, 7)</t>
         </is>
       </c>
       <c r="G77" s="4" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>After the Distortion World (decision 33)</t>
-        </is>
-      </c>
-      <c r="I77" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+          <t>After the Mansion siege: Backlot's maid shows his Egg and it hatches</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>Keep it off Cosmog's tile (35, 21)</t>
+          <t>A battle, not Renegade's Egg gift (decision 26)</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4127,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Zapdos</t>
+          <t>Articuno</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
@@ -4141,7 +4142,7 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Valley Windworks, the island</t>
+          <t>Mt. Coronet summit portal</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -4157,14 +4158,14 @@
           <t>After the Distortion World (decision 33)</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Clash</t>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>Check</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>Zekrom stands on this island until it moves to Route 215</t>
+          <t>Keep it off Cosmog's tile (35, 21)</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4175,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Moltres</t>
+          <t>Zapdos</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -4189,7 +4190,7 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Victory Road, a small room</t>
+          <t>Valley Windworks, the island</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -4205,12 +4206,16 @@
           <t>After the Distortion World (decision 33)</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J79" s="6" t="inlineStr"/>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>Clash</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>Zekrom stands on this island until it moves to Route 215</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -4218,7 +4223,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Lugia</t>
+          <t>Moltres</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
@@ -4233,7 +4238,7 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Route 220 island</t>
+          <t>Victory Road, a small room</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -4242,11 +4247,11 @@
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>After the Hall of Fame, Silver Wing</t>
+          <t>After the Distortion World (decision 33)</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
@@ -4262,7 +4267,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Ho-Oh</t>
+          <t>Lugia</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
@@ -4277,7 +4282,7 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Lost Tower top floor (5F)</t>
+          <t>Route 220 island</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4290,19 +4295,15 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>After the Hall of Fame, Rainbow Wing</t>
-        </is>
-      </c>
-      <c r="I81" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="J81" s="6" t="inlineStr">
-        <is>
-          <t>Yveltal has moved out. Keep the portal off Totem Marowak's tile (3, 4)</t>
-        </is>
-      </c>
+          <t>After the Hall of Fame, Silver Wing</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -4310,7 +4311,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Celebi</t>
+          <t>Ho-Oh</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
@@ -4325,7 +4326,7 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Eterna Forest portals</t>
+          <t>Lost Tower top floor (5F)</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -4334,11 +4335,11 @@
         </is>
       </c>
       <c r="G82" s="4" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>Renegade's trigger</t>
+          <t>After the Hall of Fame, Rainbow Wing</t>
         </is>
       </c>
       <c r="I82" s="8" t="inlineStr">
@@ -4348,7 +4349,7 @@
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>Keep the portals off Virizion (80, 10), Xerneas (70, 14) and Totem Vikavolt (22, 68)</t>
+          <t>Yveltal has moved out. Keep the portal off Totem Marowak's tile (3, 4)</t>
         </is>
       </c>
     </row>
@@ -4358,43 +4359,47 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Totem Gumshoos</t>
-        </is>
-      </c>
-      <c r="C83" s="13" t="inlineStr">
-        <is>
-          <t>Totem trial</t>
+          <t>Celebi</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>Renegade (not ported yet)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Totem</t>
+          <t>Renegade</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Route 205 South, flower bed</t>
+          <t>Eterna Forest portals</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>(197, 656)</t>
+          <t>to place</t>
         </is>
       </c>
       <c r="G83" s="4" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>After Roark</t>
-        </is>
-      </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J83" s="6" t="inlineStr"/>
+          <t>Renegade's trigger</t>
+        </is>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>Keep the portals off Virizion (80, 10), Xerneas (70, 14) and Totem Vikavolt (22, 68)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -4402,7 +4407,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Totem Ribombee</t>
+          <t>Totem Gumshoos</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
@@ -4417,32 +4422,28 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Floaroma Meadow</t>
+          <t>Route 205 South, flower bed</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>(18, 43)</t>
+          <t>(197, 656)</t>
         </is>
       </c>
       <c r="G84" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>After Mars (Valley Windworks)</t>
-        </is>
-      </c>
-      <c r="I84" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="J84" s="6" t="inlineStr">
-        <is>
-          <t>Tapu Bulu (24, 36) on the same map, post-game</t>
-        </is>
-      </c>
+          <t>After Roark</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -4450,7 +4451,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Totem Vikavolt</t>
+          <t>Totem Ribombee</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
@@ -4465,20 +4466,20 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>Eterna Forest, clearing</t>
+          <t>Floaroma Meadow</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>(22, 68)</t>
+          <t>(18, 43)</t>
         </is>
       </c>
       <c r="G85" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>After Mars</t>
+          <t>After Mars (Valley Windworks)</t>
         </is>
       </c>
       <c r="I85" s="8" t="inlineStr">
@@ -4488,7 +4489,7 @@
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>Virizion and Xerneas post-game; far apart on the map</t>
+          <t>Tapu Bulu (24, 36) on the same map, post-game</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4499,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Totem Mimikyu</t>
+          <t>Totem Vikavolt</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
@@ -4513,20 +4514,20 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Old Chateau dining area</t>
+          <t>Eterna Forest, clearing</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>(26, 10)</t>
+          <t>(22, 68)</t>
         </is>
       </c>
       <c r="G86" s="4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>After Jupiter (Eterna)</t>
+          <t>After Mars</t>
         </is>
       </c>
       <c r="I86" s="8" t="inlineStr">
@@ -4536,7 +4537,7 @@
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>Marshadow (21, 9) in the same room, post-game</t>
+          <t>Virizion and Xerneas post-game; far apart on the map</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4547,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Totem Marowak (Alolan)</t>
+          <t>Totem Mimikyu</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
@@ -4561,20 +4562,20 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Lost Tower 5F, left of the stairs</t>
+          <t>Old Chateau dining area</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>(3, 4)</t>
+          <t>(26, 10)</t>
         </is>
       </c>
       <c r="G87" s="4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>Relic Badge</t>
+          <t>After Jupiter (Eterna)</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
@@ -4584,7 +4585,7 @@
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>Ho-Oh's portal goes on this floor (not ported yet). Yveltal moved out</t>
+          <t>Marshadow (21, 9) in the same room, post-game</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4595,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Totem Raticate (Alolan)</t>
+          <t>Totem Marowak (Alolan)</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
@@ -4609,28 +4610,32 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Galactic Warehouse, lower hall</t>
+          <t>Lost Tower 5F, left of the stairs</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>(13, 10)</t>
+          <t>(3, 4)</t>
         </is>
       </c>
       <c r="G88" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
           <t>Relic Badge</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J88" s="6" t="inlineStr"/>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>Ho-Oh's portal goes on this floor (not ported yet). Yveltal moved out</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -4638,7 +4643,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Totem Lurantis</t>
+          <t>Totem Raticate (Alolan)</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
@@ -4653,20 +4658,20 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Great Marsh Area 3</t>
+          <t>Galactic Warehouse, lower hall</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>(54, 84)</t>
+          <t>(13, 10)</t>
         </is>
       </c>
       <c r="G89" s="4" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>Cobble Badge (Safari Game)</t>
+          <t>Relic Badge</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
@@ -4682,7 +4687,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Totem Araquanid</t>
+          <t>Totem Lurantis</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
@@ -4697,32 +4702,28 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Route 213, beach below the hotel</t>
+          <t>Great Marsh Area 3</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>(713, 826)</t>
+          <t>(54, 84)</t>
         </is>
       </c>
       <c r="G90" s="4" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>Fen Badge</t>
-        </is>
-      </c>
-      <c r="I90" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="J90" s="6" t="inlineStr">
-        <is>
-          <t>Suicune (689, 826) on the same route, 24 tiles west</t>
-        </is>
-      </c>
+          <t>Cobble Badge (Safari Game)</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -4730,7 +4731,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Totem Salazzle</t>
+          <t>Totem Araquanid</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
@@ -4745,20 +4746,20 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Fuego Ironworks outside, north of the yard</t>
+          <t>Route 213, beach below the hotel</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>(181, 585)</t>
+          <t>(713, 826)</t>
         </is>
       </c>
       <c r="G91" s="4" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>After Cyrus (Celestic)</t>
+          <t>Fen Badge</t>
         </is>
       </c>
       <c r="I91" s="8" t="inlineStr">
@@ -4768,7 +4769,7 @@
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>Chi-Yu (180, 593) and its stakes on the same map, post-game</t>
+          <t>Suicune (689, 826) on the same route, 24 tiles west</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4779,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Totem Kommo-o</t>
+          <t>Totem Salazzle</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
@@ -4793,28 +4794,32 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>Mt. Coronet 6F</t>
+          <t>Fuego Ironworks outside, north of the yard</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>(5, 13)</t>
+          <t>(181, 585)</t>
         </is>
       </c>
       <c r="G92" s="4" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>After Saturn (Galactic HQ)</t>
-        </is>
-      </c>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J92" s="6" t="inlineStr"/>
+          <t>After Cyrus (Celestic)</t>
+        </is>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>Chi-Yu (180, 593) and its stakes on the same map, post-game</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -4822,43 +4827,87 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
+          <t>Totem Kommo-o</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>Totem trial</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Totem</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Mt. Coronet 6F</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>(5, 13)</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>After Saturn (Galactic HQ)</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
           <t>Totem Togedemaru</t>
         </is>
       </c>
-      <c r="C93" s="13" t="inlineStr">
+      <c r="C94" s="13" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t>Totem</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E94" s="6" t="inlineStr">
         <is>
           <t>Vista Lighthouse, top floor</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="F94" s="4" t="inlineStr">
         <is>
           <t>(10, 7)</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G94" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="H93" s="6" t="inlineStr">
+      <c r="H94" s="6" t="inlineStr">
         <is>
           <t>After the Distortion World</t>
         </is>
       </c>
-      <c r="I93" s="8" t="inlineStr">
+      <c r="I94" s="8" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="J93" s="6" t="inlineStr">
+      <c r="J94" s="6" t="inlineStr">
         <is>
           <t>Victini (2, 7) on the same floor, post-game</t>
         </is>

--- a/docs/StaticEncounters.xlsx
+++ b/docs/StaticEncounters.xlsx
@@ -187,10 +187,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1553,12 +1553,12 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Stark Mountain room 1</t>
+          <t>Stark Mountain room 2, north-east dead-end tunnel</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>(34, 24)</t>
+          <t>(73, 15)</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
@@ -1569,14 +1569,14 @@
           <t>Kalos Chronicle open</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Clash</t>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>Shares room 1 with Groudon (6, 6) and the first-visit Galactic scene. Move one</t>
+          <t>MOVED 2026-10-24 from room 1 (34, 24), which Groudon uses. Room 2 has trainers and Buck's escort, but the tunnel is a dead end</t>
         </is>
       </c>
     </row>
@@ -3833,14 +3833,14 @@
           <t>After the Hall of Fame (Steven's Orbs)</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>Clash</t>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>Shares room 1 with Volcanion (34, 24)</t>
+          <t>Volcanion moved to room 2 on 2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4910,22 +4910,22 @@
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>Stark Mountain room 1</t>
+          <t>Stark Mountain</t>
         </is>
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>Volcanion (34, 24); Groudon (6, 6); first-visit Galactic scene</t>
+          <t>Groudon (room 1, 6, 6); Volcanion (room 2, 73, 15); Heatran (room 3)</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>Clash</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t>Move Volcanion or Groudon</t>
+          <t>Settled 2026-10-24: Volcanion moved to room 2</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
           <t>Jirachi (Room 7, 5, 3); Hoopa (Room 6 north-west dead end, 2, 3)</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -4962,7 +4962,7 @@
           <t>Giratina (its room); Eternatus (Victory Road B1F, 14, 19)</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -4984,7 +4984,7 @@
           <t>Landorus (782, 323, outside); Regidrago (Rock Peak Ruins doorway room, 5, 6)</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -5006,7 +5006,7 @@
           <t>Zekrom (236, 650); Zapdos portal (to place)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Clash</t>
         </is>
@@ -5402,7 +5402,7 @@
           <t>Enamorus (912, 535); Pecharunt (898, 526); Shaymin tablet (908, 491)</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -5424,7 +5424,7 @@
           <t>Yveltal (813, 426); Gene (827, 438)</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/docs/StaticEncounters.xlsx
+++ b/docs/StaticEncounters.xlsx
@@ -3275,7 +3275,7 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Regirock, Regice, Registeel in the party</t>
+          <t>After the Hall of Fame; Regirock, Regice, Registeel in the party</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
@@ -3283,7 +3283,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="J59" s="6" t="inlineStr"/>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>Renegade's story scene (Candice, Maylene, HM08) stands beside it before the Gym (decision 29)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">

--- a/docs/StaticEncounters.xlsx
+++ b/docs/StaticEncounters.xlsx
@@ -620,7 +620,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1092,12 +1091,12 @@
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>Clash</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Zapdos's Renegade portal is on this island. Decision 34: Zekrom moves to Route 215 (tile to pick)</t>
+          <t>Zapdos stands on the small north island (241, 644), not this one (E10 part 27). Decision 34 (move to Route 215, tile to pick) still stands</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1816,7 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>Articuno's Renegade summit portal goes nearby: keep it off (35, 21)</t>
+          <t>Articuno (33, 20) stands two tiles away (E10 part 27)</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2296,7 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>MOVED 2026-10-24 from Turnback Cave's Giratina room (8, 13). Shares the island with the TM59 ball (13, 18); Moltres's portal is in a 1F room</t>
+          <t>MOVED 2026-10-24 from Turnback Cave's Giratina room (8, 13). Shares the island with the TM59 ball (13, 18); Moltres stands on 2F (20, 3)</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2532,7 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Inside map; Zekrom/Zapdos are on the outside map</t>
+          <t>Inside map; Zekrom and Zapdos are on the outside map</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4135,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Renegade (not ported yet)</t>
+          <t>Renegade (ported)</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -4146,12 +4145,12 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Mt. Coronet summit portal</t>
+          <t>Mt. Coronet outside north, top snowfield</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>to place</t>
+          <t>(33, 20)</t>
         </is>
       </c>
       <c r="G78" s="4" t="n">
@@ -4169,7 +4168,7 @@
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>Keep it off Cosmog's tile (35, 21)</t>
+          <t>E10 part 27. Two tiles from Cosmog (35, 21), on its own hidden flag; Renegade's portal was at (35, 20)</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4183,7 @@
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Renegade (not ported yet)</t>
+          <t>Renegade (ported)</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4194,12 +4193,12 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Valley Windworks, the island</t>
+          <t>Valley Windworks outside, the small island north of the building (Surf)</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>to place</t>
+          <t>(241, 644)</t>
         </is>
       </c>
       <c r="G79" s="4" t="n">
@@ -4212,12 +4211,12 @@
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>Clash</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>Zekrom stands on this island until it moves to Route 215</t>
+          <t>E10 part 27. Beside the TM24 ball (242, 644), Renegade's portal tile; Zekrom (236, 650) is on the west island</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4231,7 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Renegade (not ported yet)</t>
+          <t>Renegade (ported)</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4242,12 +4241,12 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Victory Road, a small room</t>
+          <t>Victory Road 2F, the small room past the Strength boulders</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>to place</t>
+          <t>(20, 3)</t>
         </is>
       </c>
       <c r="G80" s="4" t="n">
@@ -4260,10 +4259,14 @@
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J80" s="6" t="inlineStr"/>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>E10 part 27. Off the tiles the boulder puzzle for TM79 needs (column 19 and (18, 3)); Renegade removed the boulders and used (18, 3)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -5056,17 +5059,17 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Zekrom (236, 650); Zapdos portal (to place)</t>
+          <t>Zekrom (236, 650, west island); Zapdos (241, 644, north island)</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>Clash</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>Move Zekrom to Route 215 (decision 34; tile to pick)</t>
+          <t>Different islands (E10 part 27). Decision 34 still moves Zekrom to Route 215 (tile to pick)</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5081,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Kyurem (Iceberg doorway room, 7, 5); Regice's ruins; Cosmog (35, 21); Articuno portal (to place); Kyogre (B1F); Totem Kommo-o (6F)</t>
+          <t>Kyurem (Iceberg doorway room, 7, 5); Regice's ruins; Cosmog (35, 21); Articuno (33, 20); Kyogre (B1F); Totem Kommo-o (6F)</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
@@ -5088,7 +5091,7 @@
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Kyurem works through a condition. Keep Articuno's portal off Cosmog's tile</t>
+          <t>Kyurem works through a condition. Articuno stands two tiles from Cosmog (E10 part 27)</t>
         </is>
       </c>
     </row>

--- a/docs/StaticEncounters.xlsx
+++ b/docs/StaticEncounters.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Shares the forest with Xerneas (70, 14) and Totem Vikavolt (22, 68); Celebi's Renegade portals still to place</t>
+          <t>Shares the forest with Xerneas (70, 14), Totem Vikavolt (22, 68) and Celebi (70, 58) with its portals (E10 part 28)</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Same forest as Virizion (80, 10) and Totem Vikavolt; Celebi's portals still to place</t>
+          <t>Same forest as Virizion (80, 10), Totem Vikavolt and Celebi (70, 58)</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Renegade (not ported yet)</t>
+          <t>Renegade (ported)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Eterna Forest portals</t>
+          <t>Eterna Forest, near the middle</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>to place</t>
+          <t>(70, 58)</t>
         </is>
       </c>
       <c r="G83" s="4" t="n">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>Renegade's trigger</t>
+          <t>GS Ball from Celestic Town, then the eight time portals</t>
         </is>
       </c>
       <c r="I83" s="8" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>Keep the portals off Virizion (80, 10), Xerneas (70, 14) and Totem Vikavolt (22, 68)</t>
+          <t>E10 part 28. Portals at (74, 32), (65, 34), (82, 46), (81, 72), (53, 60), (41, 58), (29, 64), (24, 68), all clear of Virizion, Xerneas and Totem Vikavolt</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Virizion (80, 10); Xerneas (70, 14); Totem Vikavolt (22, 68); Celebi portals (to place)</t>
+          <t>Virizion (80, 10); Xerneas (70, 14); Totem Vikavolt (22, 68); Celebi (70, 58) and its eight time portals</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>Place Celebi's portals clear of all three</t>
+          <t>Settled in E10 part 28: the portals keep Renegade's tiles, clear of all three (the one beside Totem Vikavolt moved to (24, 68))</t>
         </is>
       </c>
     </row>

--- a/docs/StaticEncounters.xlsx
+++ b/docs/StaticEncounters.xlsx
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>MOVED 2026-10-24 from Lost Tower 5F (13, 14), which holds Totem Marowak and Ho-Oh's planned portal. Next to the Reaper Cloth ball (816, 426); Gene at (827, 438)</t>
+          <t>MOVED 2026-10-24 from Lost Tower 5F (13, 14), which holds Totem Marowak and Ho-Oh (7, 12). Next to the Reaper Cloth ball (816, 426); Gene at (827, 438)</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Renegade (not ported yet)</t>
+          <t>Renegade (ported)</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Route 220 island</t>
+          <t>Route 220, the sandbar island at the bottom (Surf)</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>to place</t>
+          <t>(190, 921)</t>
         </is>
       </c>
       <c r="G81" s="4" t="n">
@@ -4310,7 +4310,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="J81" s="6" t="inlineStr"/>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>E10 part 29. Oak gives the Silver Wing with Articuno, Zapdos and Moltres in the party</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -4323,7 +4327,7 @@
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>Renegade (not ported yet)</t>
+          <t>Renegade (ported)</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4333,12 +4337,12 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Lost Tower top floor (5F)</t>
+          <t>Lost Tower 5F, below the old women's graves</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>to place</t>
+          <t>(7, 12)</t>
         </is>
       </c>
       <c r="G82" s="4" t="n">
@@ -4356,7 +4360,7 @@
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>Yveltal has moved out. Keep the portal off Totem Marowak's tile (3, 4)</t>
+          <t>E10 part 29. Clear of Totem Marowak's tile (3, 4). Oak gives the Rainbow Wing with Raikou, Entei and Suicune in the party</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4644,7 @@
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>Ho-Oh's portal goes on this floor (not ported yet). Yveltal moved out</t>
+          <t>Ho-Oh stands on this floor at (7, 12), after the Hall of Fame (E10 part 29). Yveltal moved out</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5129,7 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Totem Marowak (3, 4); Ho-Oh portal (to place)</t>
+          <t>Totem Marowak (3, 4); Ho-Oh (7, 12)</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
@@ -5135,7 +5139,7 @@
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Settled for Yveltal (moved 2026-10-24). Keep Ho-Oh off (3, 4)</t>
+          <t>Settled for Yveltal (moved 2026-10-24). Ho-Oh stands at (7, 12), clear of Marowak (E10 part 29)</t>
         </is>
       </c>
     </row>

--- a/docs/StaticEncounters.xlsx
+++ b/docs/StaticEncounters.xlsx
@@ -3366,11 +3366,11 @@
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Member Card</t>
+          <t>Member Card (Route 217 woman, Lunar Wing)</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Azure Flute</t>
+          <t>Azure Flute (Foreign Building elder, 16 Plates)</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">

--- a/docs/StaticEncounters.xlsx
+++ b/docs/StaticEncounters.xlsx
@@ -94,11 +94,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4B6B6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
@@ -109,12 +104,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F2DCDB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2DCDB"/>
+        <fgColor rgb="00F4B6B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,19 +166,13 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,9 +184,6 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -202,7 +193,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -214,16 +205,16 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1089,7 +1080,7 @@
           <t>Dark Stone in the bag, night</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -1409,12 +1400,12 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Wayward Cave B1F, north alcove</t>
+          <t>Wayward Cave B1F, north-west alcove</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>(21, 4)</t>
+          <t>(12, 4)</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
@@ -1425,14 +1416,14 @@
           <t>Xerneas and Yveltal caught</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>Mira's Renegade quest is in Wayward Cave; check her path</t>
+          <t>MOVED 2026-10-25 from (21, 4): that alcove lies under a bike bridge and can't be reached. Mira's quest is on 1F</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1567,7 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>MOVED 2026-10-24 from room 1 (34, 24), which Groudon uses. Room 2 has trainers and Buck's escort, but the tunnel is a dead end</t>
+          <t>MOVED 2026-10-24 from room 1 (34, 24), which Groudon uses. Room 2 has trainers and Buck's escort, but the tunnel is a dead end. The hidden Iron it stood on moved a tile east (2026-10-25)</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1592,12 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Route 222, east sand strip</t>
+          <t>Route 222, east end of the sand strip</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>(808, 795)</t>
+          <t>(813, 795)</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
@@ -1624,7 +1615,7 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Xurkitree rare roll has no tile</t>
+          <t>MOVED 2026-10-25 from (808, 795), which blocked the only way to the Quick Ball and three hidden items. Xurkitree rare roll has no tile</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3056,7 @@
           <t>Uxie / Mesprit / Azelf</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3109,7 +3100,7 @@
           <t>Dialga / Palkia</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3153,7 +3144,7 @@
           <t>Giratina</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3201,7 +3192,7 @@
           <t>Heatran</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3249,7 +3240,7 @@
           <t>Regigigas</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3297,7 +3288,7 @@
           <t>Cresselia</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3345,7 +3336,7 @@
           <t>Darkrai</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3389,7 +3380,7 @@
           <t>Shaymin</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3437,7 +3428,7 @@
           <t>Arceus</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3481,7 +3472,7 @@
           <t>Rotom</t>
         </is>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3529,7 +3520,7 @@
           <t>Raikou</t>
         </is>
       </c>
-      <c r="C65" s="11" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3573,7 +3564,7 @@
           <t>Entei</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3621,7 +3612,7 @@
           <t>Suicune</t>
         </is>
       </c>
-      <c r="C67" s="11" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3669,7 +3660,7 @@
           <t>Regirock / Regice / Registeel</t>
         </is>
       </c>
-      <c r="C68" s="11" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3717,7 +3708,7 @@
           <t>Latias / Latios</t>
         </is>
       </c>
-      <c r="C69" s="11" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3765,7 +3756,7 @@
           <t>Kyogre</t>
         </is>
       </c>
-      <c r="C70" s="11" t="inlineStr">
+      <c r="C70" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3809,7 +3800,7 @@
           <t>Groudon</t>
         </is>
       </c>
-      <c r="C71" s="11" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3857,7 +3848,7 @@
           <t>Rayquaza</t>
         </is>
       </c>
-      <c r="C72" s="11" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3905,7 +3896,7 @@
           <t>Mewtwo</t>
         </is>
       </c>
-      <c r="C73" s="11" t="inlineStr">
+      <c r="C73" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3949,7 +3940,7 @@
           <t>Jirachi</t>
         </is>
       </c>
-      <c r="C74" s="11" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3997,7 +3988,7 @@
           <t>Deoxys</t>
         </is>
       </c>
-      <c r="C75" s="11" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4041,7 +4032,7 @@
           <t>Mew</t>
         </is>
       </c>
-      <c r="C76" s="11" t="inlineStr">
+      <c r="C76" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4085,7 +4076,7 @@
           <t>Manaphy</t>
         </is>
       </c>
-      <c r="C77" s="11" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4133,7 +4124,7 @@
           <t>Articuno</t>
         </is>
       </c>
-      <c r="C78" s="12" t="inlineStr">
+      <c r="C78" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4181,7 +4172,7 @@
           <t>Zapdos</t>
         </is>
       </c>
-      <c r="C79" s="12" t="inlineStr">
+      <c r="C79" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4209,7 +4200,7 @@
           <t>After the Distortion World (decision 33)</t>
         </is>
       </c>
-      <c r="I79" s="9" t="inlineStr">
+      <c r="I79" s="8" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -4229,7 +4220,7 @@
           <t>Moltres</t>
         </is>
       </c>
-      <c r="C80" s="12" t="inlineStr">
+      <c r="C80" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4257,7 +4248,7 @@
           <t>After the Distortion World (decision 33)</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
+      <c r="I80" s="8" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -4277,7 +4268,7 @@
           <t>Lugia</t>
         </is>
       </c>
-      <c r="C81" s="12" t="inlineStr">
+      <c r="C81" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4325,7 +4316,7 @@
           <t>Ho-Oh</t>
         </is>
       </c>
-      <c r="C82" s="12" t="inlineStr">
+      <c r="C82" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4373,7 +4364,7 @@
           <t>Celebi</t>
         </is>
       </c>
-      <c r="C83" s="12" t="inlineStr">
+      <c r="C83" s="10" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4421,7 +4412,7 @@
           <t>Totem Gumshoos</t>
         </is>
       </c>
-      <c r="C84" s="13" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4465,7 +4456,7 @@
           <t>Totem Ribombee</t>
         </is>
       </c>
-      <c r="C85" s="13" t="inlineStr">
+      <c r="C85" s="11" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4513,7 +4504,7 @@
           <t>Totem Vikavolt</t>
         </is>
       </c>
-      <c r="C86" s="13" t="inlineStr">
+      <c r="C86" s="11" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4561,7 +4552,7 @@
           <t>Totem Mimikyu</t>
         </is>
       </c>
-      <c r="C87" s="13" t="inlineStr">
+      <c r="C87" s="11" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4609,7 +4600,7 @@
           <t>Totem Marowak (Alolan)</t>
         </is>
       </c>
-      <c r="C88" s="13" t="inlineStr">
+      <c r="C88" s="11" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4657,7 +4648,7 @@
           <t>Totem Raticate (Alolan)</t>
         </is>
       </c>
-      <c r="C89" s="13" t="inlineStr">
+      <c r="C89" s="11" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4701,7 +4692,7 @@
           <t>Totem Lurantis</t>
         </is>
       </c>
-      <c r="C90" s="13" t="inlineStr">
+      <c r="C90" s="11" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4745,7 +4736,7 @@
           <t>Totem Araquanid</t>
         </is>
       </c>
-      <c r="C91" s="13" t="inlineStr">
+      <c r="C91" s="11" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4793,7 +4784,7 @@
           <t>Totem Salazzle</t>
         </is>
       </c>
-      <c r="C92" s="13" t="inlineStr">
+      <c r="C92" s="11" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4841,7 +4832,7 @@
           <t>Totem Kommo-o</t>
         </is>
       </c>
-      <c r="C93" s="13" t="inlineStr">
+      <c r="C93" s="11" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4885,7 +4876,7 @@
           <t>Totem Togedemaru</t>
         </is>
       </c>
-      <c r="C94" s="13" t="inlineStr">
+      <c r="C94" s="11" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4946,550 +4937,550 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Map</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Encounters there</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>What to do</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Stark Mountain</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Groudon (room 1, 6, 6); Volcanion (room 2, 73, 15); Heatran (room 3)</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>Settled 2026-10-24: Volcanion moved to room 2</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Solaceon Ruins</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Jirachi (Room 7, 5, 3); Hoopa (Room 6 north-west dead end, 2, 3)</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Settled 2026-10-24: Hoopa moved to Room 6</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Turnback Cave / Victory Road B1F</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Giratina (its room); Eternatus (Victory Road B1F, 14, 19)</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Settled 2026-10-24: Eternatus moved to Victory Road B1F</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Route 228</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Landorus (782, 323, outside); Regidrago (Rock Peak Ruins doorway room, 5, 6)</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Settled 2026-10-24: Landorus moved to the sand field</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Valley Windworks outside</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Zekrom (236, 650, west island); Zapdos (241, 644, north island)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Different islands (E10 part 27). Decision 34 still moves Zekrom to Route 215 (tile to pick)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Mt. Coronet</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Kyurem (Iceberg doorway room, 7, 5); Regice's ruins; Cosmog (35, 21); Articuno (33, 20); Kyogre (B1F); Totem Kommo-o (6F)</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Kyurem works through a condition. Articuno stands two tiles from Cosmog (E10 part 27)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Eterna Forest</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Virizion (80, 10); Xerneas (70, 14); Totem Vikavolt (22, 68); Celebi (70, 58) and its eight time portals</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Settled in E10 part 28: the portals keep Renegade's tiles, clear of all three (the one beside Totem Vikavolt moved to (24, 68))</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Lost Tower 5F</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Totem Marowak (3, 4); Ho-Oh (7, 12)</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Settled for Yveltal (moved 2026-10-24). Ho-Oh stands at (7, 12), clear of Marowak (E10 part 29)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Old Chateau dining area</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Totem Mimikyu (26, 10); Marshadow (21, 9)</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Both stand only if the Totem trial was skipped. Different eras of play</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Vista Lighthouse top floor</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Totem Togedemaru (10, 7); Victini (2, 7); Electric Master (4, 3)</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>As above</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Fuego Ironworks outside</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Totem Salazzle (181, 585); Chi-Yu (180, 593) and stakes 7–8</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>As above</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Floaroma Meadow</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Totem Ribombee (18, 43); Tapu Bulu (24, 36)</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>As above</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Route 213</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Totem Araquanid (713, 826); Suicune (689, 826)</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>24 tiles apart; fine</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Route 226</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Tapu Fini (716, 345); Wyver (717, 346)</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Adjacent tiles; check the encounter can be reached</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Oreburgh Mine B2F</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Diancie (2, 22); Meltan (5, 20); Melmetal (5, 24)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Sequenced or conditional; check they don't block the path</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Fullmoon Island forest</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Tapu Lele (13, 12); Cresselia then Latias/Latios (16, 15)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Sequenced; crowded but fine</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Sendoff Spring</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>Koraidon (29, 36); Miraidon (27, 37); Terapagos (30, 34)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Check Cynthia's scene tiles</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Wayward Cave</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>Zygarde (B1F 21, 4); Necrozma (1F 70, 9); Mira's quest</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Zygarde (B1F 12, 4); Necrozma (1F 70, 9); Mira's quest</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Checked 2026-10-25: Mira waits on 1F at the hidden entrance, Zygarde is on B1F</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Sunyshore Gym, Volkner's room</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Magearna (11, 13); Volkner</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>Check Mira's path</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Sunyshore Gym, Volkner's room</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Magearna (11, 13); Volkner</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Check the rematch and exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Veilstone Gym</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Kubfu (13, 17); the Gym puzzle</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>Check the rematch and exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>Veilstone Gym</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>Kubfu (13, 17); the Gym puzzle</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Check the puzzle</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Celestic Town</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Calyrex (461, 527); the elder, the ruins path</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>Check the puzzle</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Celestic Town</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Calyrex (461, 527); the elder, the ruins path</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Check the ruins path</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Contest Hall stage</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Meloetta (27, 8)</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>Check the ruins path</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Contest Hall stage</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>Meloetta (27, 8)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Check it never shows during a contest</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Route 224</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Enamorus (912, 535); Pecharunt (898, 526); Shaymin tablet (908, 491)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Settled 2026-10-24: Enamorus moved off the tablet</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Route 229</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>Yveltal (813, 426); Gene (827, 438)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Yveltal's new spot (2026-10-24)</t>
         </is>
@@ -5514,132 +5505,132 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="B1" s="20" t="inlineStr"/>
+      <c r="B1" s="17" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Clash</t>
         </is>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Two encounters (or an encounter and a story scene) share a small room or tile and can stand at once. Must be settled.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Shares a map with another encounter, NPC or puzzle. Verify the tiles or timing in game.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Nothing found on the map.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr"/>
-      <c r="B5" s="20" t="inlineStr"/>
+      <c r="A5" s="16" t="inlineStr"/>
+      <c r="B5" s="17" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
+      <c r="B6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Chronicle</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Post-game Chronicles from the Legend Archivist (Canalave Library 2F).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Platinum's own legendaries.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Renegade Platinum's events already ported (E10).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Renegade (not ported yet)</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Renegade's events still to port.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Story Totem trials (data/totem_trials.yaml). Each hides once its trial is done.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr"/>
-      <c r="B12" s="20" t="inlineStr"/>
+      <c r="A12" s="16" t="inlineStr"/>
+      <c r="B12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>docs/LegendaryTriggers.md, docs/LegendaryPlacementReview.md, data/totem_trials.yaml, decomp/res/field/events/*.json</t>
         </is>

--- a/docs/StaticEncounters.xlsx
+++ b/docs/StaticEncounters.xlsx
@@ -51,17 +51,17 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -89,11 +89,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4A8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
@@ -110,6 +105,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4B6B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4A8"/>
       </patternFill>
     </fill>
     <fill>
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,7 +163,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -172,31 +172,25 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -205,16 +199,16 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -600,7 +594,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sovereign Platinum: static encounters, including Totems (2026-10-24)</t>
+          <t>Sovereign Platinum: static encounters, including Totems (2026-10-25)</t>
         </is>
       </c>
     </row>
@@ -796,14 +790,14 @@
           <t>Unova Chronicle open</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Shares the forest with Xerneas (70, 14), Totem Vikavolt (22, 68) and Celebi (70, 58) with its portals (E10 part 28)</t>
+          <t>Tile check 2026-10-25: clear. Shares the forest with Xerneas (70, 14), Totem Vikavolt (22, 68) and Celebi (70, 58) with its portals (E10 part 28)</t>
         </is>
       </c>
     </row>
@@ -888,14 +882,14 @@
           <t>Unova Chronicle open</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Same floor as Totem Togedemaru (10, 7) and the Electric Master (4, 3). Fine once the Totem trial is done; both stand if the trial was skipped</t>
+          <t>Tile check 2026-10-25: clear. Same floor as Totem Togedemaru (10, 7) and the Electric Master (4, 3); reachable even while both stand</t>
         </is>
       </c>
     </row>
@@ -936,14 +930,14 @@
           <t>Composer hears Sing</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Uses the no-contest stage map; check it never shows during a contest</t>
+          <t>Contests use their own stage map (CONTEST_HALL_STAGE_ONGOING_CONTEST), so it never shows during one. Tile check 2026-10-25: clear.</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1058,12 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Valley Windworks outside, the island (moving)</t>
+          <t>Route 215, the north-west loop by the big tree</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>(236, 650)</t>
+          <t>(590, 578)</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
@@ -1080,14 +1074,14 @@
           <t>Dark Stone in the bag, night</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Zapdos stands on the small north island (241, 644), not this one (E10 part 27). Decision 34 (move to Route 215, tile to pick) still stands</t>
+          <t>MOVED 2026-10-25 from Valley Windworks' island (236, 650), decision 34. Tile check: clear</t>
         </is>
       </c>
     </row>
@@ -1128,14 +1122,14 @@
           <t>Reshiram and Zekrom caught; no Relicanth+Wailord pair</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>The Relicanth/Wailord pair swaps this room to Regice's chamber. Works through a condition, but fragile</t>
+          <t>The Relicanth/Wailord pair sends the doorway to Regice's chamber; without the pair it leads here. Works as designed (checked 2026-10-25)</t>
         </is>
       </c>
     </row>
@@ -1320,14 +1314,14 @@
           <t>Kalos Chronicle open</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Same forest as Virizion (80, 10), Totem Vikavolt and Celebi (70, 58)</t>
+          <t>Tile check 2026-10-25: clear. Same forest as Virizion (80, 10), Totem Vikavolt and Celebi (70, 58)</t>
         </is>
       </c>
     </row>
@@ -1464,14 +1458,14 @@
           <t>Carbink in the party</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Meltan (5, 20) and Melmetal (5, 24) within 4 tiles; check none blocks the path</t>
+          <t>Tile check 2026-10-25: clear. Meltan (5, 20) and Melmetal (5, 24) within 4 tiles; none blocks the path</t>
         </is>
       </c>
     </row>
@@ -1656,14 +1650,14 @@
           <t>Alola Chronicle open</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Three tiles from Cresselia's / the Lati rock's tile (16, 15). Sequenced, but crowded</t>
+          <t>Tile check 2026-10-25: clear. Three tiles from Cresselia's / the Lati rock's tile (16, 15), which are sequenced</t>
         </is>
       </c>
     </row>
@@ -1704,14 +1698,14 @@
           <t>Alola Chronicle open</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Totem Ribombee (18, 43) on the same map; the Grass Master at (47, 41)</t>
+          <t>Tile check 2026-10-25: clear. Totem Ribombee (18, 43) on the same map; the Grass Master at (47, 41)</t>
         </is>
       </c>
     </row>
@@ -1752,14 +1746,14 @@
           <t>Alola Chronicle open</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>Wyver (Renegade NPC) stands at (717, 346), the next tile. Check it doesn't block the encounter</t>
+          <t>Tile check 2026-10-25: clear. Wyver (Renegade NPC) stands at (717, 346), diagonal to it; it can be reached even with Wyver in the way</t>
         </is>
       </c>
     </row>
@@ -1800,14 +1794,14 @@
           <t>Alola Chronicle open</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>Articuno (33, 20) stands two tiles away (E10 part 27)</t>
+          <t>Tile check 2026-10-25: clear. Articuno (33, 20) stands two tiles away (E10 part 27)</t>
         </is>
       </c>
     </row>
@@ -1848,14 +1842,14 @@
           <t>Solgaleo or Lunala caught</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Mira's Renegade quest is in Wayward Cave</t>
+          <t>Tile check 2026-10-25: clear. Through the hidden entrance, past Mira's gate (her Renegade quest)</t>
         </is>
       </c>
     </row>
@@ -1944,14 +1938,14 @@
           <t>Alola Chronicle open</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Beside Volkner; check it doesn't block his rematch or the exit</t>
+          <t>Tile check 2026-10-25: clear. Beside Volkner; it blocks neither his rematch nor the exit</t>
         </is>
       </c>
     </row>
@@ -1992,14 +1986,14 @@
           <t>Alola Chronicle open</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Totem Mimikyu (26, 10) in the same room. Fine once the trial is done; both stand if it was skipped</t>
+          <t>Tile check 2026-10-25: clear. Totem Mimikyu (26, 10) in the same room; reachable even while it stands</t>
         </is>
       </c>
     </row>
@@ -2088,14 +2082,14 @@
           <t>Alola Chronicle open</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>See Diancie</t>
+          <t>Tile check 2026-10-25: clear. See Diancie</t>
         </is>
       </c>
     </row>
@@ -2136,14 +2130,14 @@
           <t>Meltan caught</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>See Diancie</t>
+          <t>Tile check 2026-10-25: clear. See Diancie</t>
         </is>
       </c>
     </row>
@@ -2328,14 +2322,14 @@
           <t>Galar Chronicle open</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Check it isn't on the path to the ruins or the elder</t>
+          <t>Tile check 2026-10-25: clear. Off the paths to the ruins and the elder</t>
         </is>
       </c>
     </row>
@@ -2424,14 +2418,14 @@
           <t>Galar Chronicle open</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Inside the Gym; check it doesn't block the punching-bag puzzle</t>
+          <t>Tile check 2026-10-25: clear. Off every punching-bag track (the Gym's track table in src/overlay008/gym_features.c)</t>
         </is>
       </c>
     </row>
@@ -2748,14 +2742,14 @@
           <t>Stakes 7 and 8 pulled</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Totem Salazzle (181, 585) on the same map, 8 tiles north</t>
+          <t>Tile check 2026-10-25: clear. Totem Salazzle (181, 585) on the same map, 8 tiles north</t>
         </is>
       </c>
     </row>
@@ -2940,14 +2934,14 @@
           <t>All ten ancient Paradox Pokémon traded</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Miraidon (27, 37) and Terapagos (30, 34) within 3 tiles; check Cynthia's scene tiles</t>
+          <t>Cynthia's Sendoff Spring scene is before the Hall of Fame, and the Paldea Chronicle opens after it, so they never meet. Tile check 2026-10-25: clear.</t>
         </is>
       </c>
     </row>
@@ -2988,9 +2982,9 @@
           <t>All ten future Paradox Pokémon traded</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
@@ -3036,9 +3030,9 @@
           <t>Koraidon and Miraidon caught</t>
         </is>
       </c>
-      <c r="I54" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
@@ -3056,7 +3050,7 @@
           <t>Uxie / Mesprit / Azelf</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3100,7 +3094,7 @@
           <t>Dialga / Palkia</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3144,7 +3138,7 @@
           <t>Giratina</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3192,7 +3186,7 @@
           <t>Heatran</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3240,7 +3234,7 @@
           <t>Regigigas</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3288,7 +3282,7 @@
           <t>Cresselia</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3316,14 +3310,14 @@
           <t>After the Lunar Wing quest</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>Tapu Lele (13, 12) three tiles away; Latias/Latios take the same tile later</t>
+          <t>Tapu Lele (13, 12) three tiles away; Latias/Latios take the same tile only after Cresselia (sequenced). Tile check 2026-10-25: clear.</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3330,7 @@
           <t>Darkrai</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3380,7 +3374,7 @@
           <t>Shaymin</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3428,7 +3422,7 @@
           <t>Arceus</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3472,7 +3466,7 @@
           <t>Rotom</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
@@ -3520,7 +3514,7 @@
           <t>Raikou</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3564,7 +3558,7 @@
           <t>Entei</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3612,7 +3606,7 @@
           <t>Suicune</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3640,14 +3634,14 @@
           <t>After the Distortion World</t>
         </is>
       </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>Totem Araquanid (713, 826) on the same route, 24 tiles east</t>
+          <t>Tile check 2026-10-25: clear. Totem Araquanid (713, 826) on the same route, 24 tiles east</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3654,7 @@
           <t>Regirock / Regice / Registeel</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3688,14 +3682,14 @@
           <t>Relicanth and Wailord in the party</t>
         </is>
       </c>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>Iceberg: Kyurem's doorway room. Rock Peak is settled (Landorus moved)</t>
+          <t>Iceberg: the pair sends Mt. Coronet's doorway here instead of Kyurem's room (works as designed). Rock Peak is settled (Landorus moved)</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3702,7 @@
           <t>Latias / Latios</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3756,7 +3750,7 @@
           <t>Kyogre</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C70" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3800,7 +3794,7 @@
           <t>Groudon</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3848,7 +3842,7 @@
           <t>Rayquaza</t>
         </is>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3896,7 +3890,7 @@
           <t>Mewtwo</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3940,7 +3934,7 @@
           <t>Jirachi</t>
         </is>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C74" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -3988,7 +3982,7 @@
           <t>Deoxys</t>
         </is>
       </c>
-      <c r="C75" s="10" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4032,7 +4026,7 @@
           <t>Mew</t>
         </is>
       </c>
-      <c r="C76" s="10" t="inlineStr">
+      <c r="C76" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4076,7 +4070,7 @@
           <t>Manaphy</t>
         </is>
       </c>
-      <c r="C77" s="10" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4124,7 +4118,7 @@
           <t>Articuno</t>
         </is>
       </c>
-      <c r="C78" s="10" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4152,14 +4146,14 @@
           <t>After the Distortion World (decision 33)</t>
         </is>
       </c>
-      <c r="I78" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>E10 part 27. Two tiles from Cosmog (35, 21), on its own hidden flag; Renegade's portal was at (35, 20)</t>
+          <t>Tile check 2026-10-25: clear. E10 part 27. Two tiles from Cosmog (35, 21), on its own hidden flag; Renegade's portal was at (35, 20)</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4166,7 @@
           <t>Zapdos</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4200,14 +4194,14 @@
           <t>After the Distortion World (decision 33)</t>
         </is>
       </c>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>E10 part 27. Beside the TM24 ball (242, 644), Renegade's portal tile; Zekrom (236, 650) is on the west island</t>
+          <t>E10 part 27. Beside the TM24 ball (242, 644), Renegade's portal tile. Zekrom moved to Route 215 (2026-10-25), so the islands are Zapdos's alone. Tile check: clear</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4214,7 @@
           <t>Moltres</t>
         </is>
       </c>
-      <c r="C80" s="10" t="inlineStr">
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4248,14 +4242,14 @@
           <t>After the Distortion World (decision 33)</t>
         </is>
       </c>
-      <c r="I80" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>E10 part 27. Off the tiles the boulder puzzle for TM79 needs (column 19 and (18, 3)); Renegade removed the boulders and used (18, 3)</t>
+          <t>Tile check 2026-10-25: clear. E10 part 27. Off the tiles the boulder puzzle for TM79 needs (column 19 and (18, 3))</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4262,7 @@
           <t>Lugia</t>
         </is>
       </c>
-      <c r="C81" s="10" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4316,7 +4310,7 @@
           <t>Ho-Oh</t>
         </is>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C82" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4344,14 +4338,14 @@
           <t>After the Hall of Fame, Rainbow Wing</t>
         </is>
       </c>
-      <c r="I82" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>E10 part 29. Clear of Totem Marowak's tile (3, 4). Oak gives the Rainbow Wing with Raikou, Entei and Suicune in the party</t>
+          <t>Tile check 2026-10-25: clear. E10 part 29. Clear of Totem Marowak's tile (3, 4). Oak gives the Rainbow Wing with Raikou, Entei and Suicune in the party</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4358,7 @@
           <t>Celebi</t>
         </is>
       </c>
-      <c r="C83" s="10" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
@@ -4392,14 +4386,14 @@
           <t>GS Ball from Celestic Town, then the eight time portals</t>
         </is>
       </c>
-      <c r="I83" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>E10 part 28. Portals at (74, 32), (65, 34), (82, 46), (81, 72), (53, 60), (41, 58), (29, 64), (24, 68), all clear of Virizion, Xerneas and Totem Vikavolt</t>
+          <t>Tile check 2026-10-25: clear. E10 part 28. Its eight portals are clear of Virizion, Xerneas and Totem Vikavolt</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4406,7 @@
           <t>Totem Gumshoos</t>
         </is>
       </c>
-      <c r="C84" s="11" t="inlineStr">
+      <c r="C84" s="10" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4456,7 +4450,7 @@
           <t>Totem Ribombee</t>
         </is>
       </c>
-      <c r="C85" s="11" t="inlineStr">
+      <c r="C85" s="10" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4484,14 +4478,14 @@
           <t>After Mars (Valley Windworks)</t>
         </is>
       </c>
-      <c r="I85" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>Tapu Bulu (24, 36) on the same map, post-game</t>
+          <t>Tile check 2026-10-25: clear. Tapu Bulu (24, 36) on the same map, post-game</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4498,7 @@
           <t>Totem Vikavolt</t>
         </is>
       </c>
-      <c r="C86" s="11" t="inlineStr">
+      <c r="C86" s="10" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4532,14 +4526,14 @@
           <t>After Mars</t>
         </is>
       </c>
-      <c r="I86" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>Virizion and Xerneas post-game; far apart on the map</t>
+          <t>Tile check 2026-10-25: clear. Virizion and Xerneas post-game; far apart on the map</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4546,7 @@
           <t>Totem Mimikyu</t>
         </is>
       </c>
-      <c r="C87" s="11" t="inlineStr">
+      <c r="C87" s="10" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4580,14 +4574,14 @@
           <t>After Jupiter (Eterna)</t>
         </is>
       </c>
-      <c r="I87" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>Marshadow (21, 9) in the same room, post-game</t>
+          <t>Tile check 2026-10-25: clear. Marshadow (21, 9) in the same room, post-game</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4594,7 @@
           <t>Totem Marowak (Alolan)</t>
         </is>
       </c>
-      <c r="C88" s="11" t="inlineStr">
+      <c r="C88" s="10" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4628,14 +4622,14 @@
           <t>Relic Badge</t>
         </is>
       </c>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>Ho-Oh stands on this floor at (7, 12), after the Hall of Fame (E10 part 29). Yveltal moved out</t>
+          <t>Tile check 2026-10-25: clear. Ho-Oh stands on this floor at (7, 12), after the Hall of Fame (E10 part 29). Yveltal moved out</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4642,7 @@
           <t>Totem Raticate (Alolan)</t>
         </is>
       </c>
-      <c r="C89" s="11" t="inlineStr">
+      <c r="C89" s="10" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4692,7 +4686,7 @@
           <t>Totem Lurantis</t>
         </is>
       </c>
-      <c r="C90" s="11" t="inlineStr">
+      <c r="C90" s="10" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4736,7 +4730,7 @@
           <t>Totem Araquanid</t>
         </is>
       </c>
-      <c r="C91" s="11" t="inlineStr">
+      <c r="C91" s="10" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4764,14 +4758,14 @@
           <t>Fen Badge</t>
         </is>
       </c>
-      <c r="I91" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>Suicune (689, 826) on the same route, 24 tiles west</t>
+          <t>Tile check 2026-10-25: clear. Suicune (689, 826) on the same route, 24 tiles west</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4778,7 @@
           <t>Totem Salazzle</t>
         </is>
       </c>
-      <c r="C92" s="11" t="inlineStr">
+      <c r="C92" s="10" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4812,14 +4806,14 @@
           <t>After Cyrus (Celestic)</t>
         </is>
       </c>
-      <c r="I92" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>Chi-Yu (180, 593) and its stakes on the same map, post-game</t>
+          <t>Tile check 2026-10-25: clear. Chi-Yu (180, 593) and its stakes on the same map, post-game</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4826,7 @@
           <t>Totem Kommo-o</t>
         </is>
       </c>
-      <c r="C93" s="11" t="inlineStr">
+      <c r="C93" s="10" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4876,7 +4870,7 @@
           <t>Totem Togedemaru</t>
         </is>
       </c>
-      <c r="C94" s="11" t="inlineStr">
+      <c r="C94" s="10" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
@@ -4904,14 +4898,14 @@
           <t>After the Distortion World</t>
         </is>
       </c>
-      <c r="I94" s="8" t="inlineStr">
-        <is>
-          <t>Check</t>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
-          <t>Victini (2, 7) on the same floor, post-game</t>
+          <t>Tile check 2026-10-25: clear. Victini (2, 7) on the same floor, post-game</t>
         </is>
       </c>
     </row>
@@ -4937,550 +4931,550 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Map</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Encounters there</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>What to do</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Stark Mountain</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Groudon (room 1, 6, 6); Volcanion (room 2, 73, 15); Heatran (room 3)</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Settled 2026-10-24: Volcanion moved to room 2</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Solaceon Ruins</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Jirachi (Room 7, 5, 3); Hoopa (Room 6 north-west dead end, 2, 3)</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Settled 2026-10-24: Hoopa moved to Room 6</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Turnback Cave / Victory Road B1F</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Giratina (its room); Eternatus (Victory Road B1F, 14, 19)</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Settled 2026-10-24: Eternatus moved to Victory Road B1F</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Route 228</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Landorus (782, 323, outside); Regidrago (Rock Peak Ruins doorway room, 5, 6)</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Settled 2026-10-24: Landorus moved to the sand field</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Valley Windworks outside</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Zekrom (236, 650, west island); Zapdos (241, 644, north island)</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Different islands (E10 part 27). Decision 34 still moves Zekrom to Route 215 (tile to pick)</t>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Zapdos (241, 644, north island); Regieleki (building)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Settled 2026-10-25: Zekrom moved to Route 215 (decision 34)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Mt. Coronet</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Kyurem (Iceberg doorway room, 7, 5); Regice's ruins; Cosmog (35, 21); Articuno (33, 20); Kyogre (B1F); Totem Kommo-o (6F)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Kyurem works through a condition. Articuno stands two tiles from Cosmog (E10 part 27)</t>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Kyurem works by design: the Relicanth/Wailord pair swaps the doorway to Regice's chamber. Articuno stands two tiles from Cosmog. Tile check 2026-10-25: clear</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Eterna Forest</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Virizion (80, 10); Xerneas (70, 14); Totem Vikavolt (22, 68); Celebi (70, 58) and its eight time portals</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>Settled in E10 part 28: the portals keep Renegade's tiles, clear of all three (the one beside Totem Vikavolt moved to (24, 68))</t>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. Settled in E10 part 28: the portals keep Renegade's tiles, clear of all three (the one beside Totem Vikavolt moved to (24, 68))</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Lost Tower 5F</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Totem Marowak (3, 4); Ho-Oh (7, 12)</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Settled for Yveltal (moved 2026-10-24). Ho-Oh stands at (7, 12), clear of Marowak (E10 part 29)</t>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. Settled for Yveltal (moved 2026-10-24). Ho-Oh stands at (7, 12), clear of Marowak (E10 part 29)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Old Chateau dining area</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Totem Mimikyu (26, 10); Marshadow (21, 9)</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Both stand only if the Totem trial was skipped. Different eras of play</t>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. Both stand only if the Totem trial was skipped. Different eras of play</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Vista Lighthouse top floor</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Totem Togedemaru (10, 7); Victini (2, 7); Electric Master (4, 3)</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>As above</t>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. As above</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Fuego Ironworks outside</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Totem Salazzle (181, 585); Chi-Yu (180, 593) and stakes 7–8</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>As above</t>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. As above</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Floaroma Meadow</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Totem Ribombee (18, 43); Tapu Bulu (24, 36)</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>As above</t>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. As above</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Route 213</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Totem Araquanid (713, 826); Suicune (689, 826)</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>24 tiles apart; fine</t>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. 24 tiles apart; fine</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Route 226</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Tapu Fini (716, 345); Wyver (717, 346)</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>Adjacent tiles; check the encounter can be reached</t>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. Adjacent tiles; check the encounter can be reached</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Oreburgh Mine B2F</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Diancie (2, 22); Meltan (5, 20); Melmetal (5, 24)</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>Sequenced or conditional; check they don't block the path</t>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. Sequenced or conditional; check they don't block the path</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Fullmoon Island forest</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Tapu Lele (13, 12); Cresselia then Latias/Latios (16, 15)</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>Sequenced; crowded but fine</t>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. Sequenced; crowded but fine</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Sendoff Spring</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Koraidon (29, 36); Miraidon (27, 37); Terapagos (30, 34)</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>Check Cynthia's scene tiles</t>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. Check Cynthia's scene tiles</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Wayward Cave</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Zygarde (B1F 12, 4); Necrozma (1F 70, 9); Mira's quest</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Checked 2026-10-25: Mira waits on 1F at the hidden entrance, Zygarde is on B1F</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Sunyshore Gym, Volkner's room</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Magearna (11, 13); Volkner</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>Check the rematch and exit</t>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. Check the rematch and exit</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Veilstone Gym</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Kubfu (13, 17); the Gym puzzle</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>Check the puzzle</t>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. Check the puzzle</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Celestic Town</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Calyrex (461, 527); the elder, the ruins path</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>Check the ruins path</t>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. Check the ruins path</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Contest Hall stage</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Meloetta (27, 8)</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>Check it never shows during a contest</t>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Tile check 2026-10-25: clear. Check it never shows during a contest</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Route 224</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Enamorus (912, 535); Pecharunt (898, 526); Shaymin tablet (908, 491)</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Settled 2026-10-24: Enamorus moved off the tablet</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Route 229</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Yveltal (813, 426); Gene (827, 438)</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Yveltal's new spot (2026-10-24)</t>
         </is>
@@ -5505,132 +5499,132 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr"/>
+      <c r="B1" s="15" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Clash</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Two encounters (or an encounter and a story scene) share a small room or tile and can stand at once. Must be settled.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Shares a map with another encounter, NPC or puzzle. Verify the tiles or timing in game.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Nothing found on the map.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr"/>
-      <c r="B5" s="17" t="inlineStr"/>
+      <c r="A5" s="14" t="inlineStr"/>
+      <c r="B5" s="15" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr"/>
+      <c r="B6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Chronicle</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Post-game Chronicles from the Legend Archivist (Canalave Library 2F).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Vanilla</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Platinum's own legendaries.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Renegade (ported)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Renegade Platinum's events already ported (E10).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Renegade (not ported yet)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Renegade's events still to port.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>Totem trial</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Story Totem trials (data/totem_trials.yaml). Each hides once its trial is done.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr"/>
-      <c r="B12" s="17" t="inlineStr"/>
+      <c r="A12" s="14" t="inlineStr"/>
+      <c r="B12" s="15" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>docs/LegendaryTriggers.md, docs/LegendaryPlacementReview.md, data/totem_trials.yaml, decomp/res/field/events/*.json</t>
         </is>
